--- a/build/schedule/PO-Questions-Branko-Schedule-TechPlan_2026-07-30.xlsx
+++ b/build/schedule/PO-Questions-Branko-Schedule-TechPlan_2026-07-30.xlsx
@@ -33,48 +33,27 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -83,10 +62,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -455,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -469,7 +448,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Schedule - Questions for Branko (from the engineering plan) - 2026-07-30</t>
+          <t>Schedule - Questions for Branko - 2026-07-30 (revised 2026-07-31)</t>
         </is>
       </c>
     </row>
@@ -511,27 +490,27 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Shop closure days: does a multi-day job skip them?</t>
+          <t>Shop closure days: does a multi-day job skip them? (please confirm this still stands)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>When a big job is spread across several days, the schedule plans one shift per day. Earlier we were told that shop closure days (holidays, inventory days) do NOT get skipped in the first release - a shift can land on a closure day. The engineering build plan says the opposite: the system will really skip closure days, and the preview will show them as skipped.</t>
+          <t>When a big job is spread across several days, the schedule plans one shift per day. The current product write-up says shop closure days (holidays, inventory days) are NOT skipped in the first release - a shift can land on a closure day, and only weekends are skipped (and only when no working hours are set for them). Our tests are written that way. Two things still disagree with it: a later part of the same product write-up still says closure days stop the schedule from planning work on them, and the engineering build plan builds real closure-day skipping.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>In the first release, when a job is spread across days that include a shop closure day, should that day be skipped (no work planned on it), or can a shift land on it?</t>
+          <t>Please confirm the current write-up stands - in the first release closure days are NOT skipped - and that the other sentence in the write-up and the build plan should be corrected.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>A) Skip closure days - no shift is planned on a closure day (as the build plan says).
-B) Do not skip them - a shift can land on a closure day in the first release (as we were told earlier).
+          <t>A) Confirmed - do not skip closure days in the first release; the other sentence and the build plan should change.
+B) No - closure days should be skipped after all.
 C) Something else (please explain).</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -539,27 +518,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Does the conflict counter include double-bookings?</t>
+          <t>Where do the shop's and technicians' working hours live? (please confirm this still stands)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>The schedule flags problems like a shift outside a technician's working hours, and a counter at the top shows how many problems there are. The product write-up also counts a technician being booked on two jobs at the same time ("double-booked") as one of these problems. The engineering plan treats double-booking as a milder heads-up only - shown on the screen, but not counted as a real "conflict" in that counter.</t>
+          <t>The current product write-up says working hours are set in two places: a technician's own hours inside the "Edit Staff Member" window (behind a switch called "Set custom hours for this technician"), and the shop's hours inside the "Edit Location" window (behind "Set business hours for this shop"). Our tests are written that way. The engineering build plan instead builds a separate "Schedule Settings" page in the Administration area, which would hold the shop's hours AND its closure days.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>When a technician is booked on two jobs at the same time, should that show up in the conflicts counter and list at the top, or only as a milder warning on the shift itself?</t>
+          <t>Please confirm the current write-up stands - hours are set in Edit Staff Member and Edit Location - and tell us where the shop's closure days are set, since the write-up does not say.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>A) Yes - double-bookings count in the conflicts counter and list.
-B) No - double-bookings are only a milder warning on the shift, not in the counter.
+          <t>A) Confirmed - Edit Staff Member and Edit Location; the build plan should change. (Please say where closure days are set.)
+B) No - use a separate "Schedule Settings" page in Administration instead.
 C) Something else (please explain).</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -567,27 +546,27 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Where do the shop's working hours and closure days live?</t>
+          <t>Can a technician have a split working day (two time ranges)? (please confirm this still stands)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>The design pictures we had put the shop's working hours inside the "Edit Location" window (a toggle called "Set business hours for this shop"). The engineering plan instead builds a separate "Schedule Settings" page in the Administration area, which holds the shop's working hours AND its closure days, with a link to it from the schedule's view options.</t>
+          <t>The current product write-up says each day starts with one working time range and an "Add hours" button adds more ranges, so a technician can have a split day (for example 8-12 and then 13-17), with a red warning and a blocked Save if two ranges overlap. Our tests are written that way. The engineering build plan stores only ONE working range per day for each technician - no second range at all.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Where should someone go to set the shop's working hours and closure days?</t>
+          <t>Please confirm the current write-up stands - a technician's day can have more than one working range in the first release - and that the build plan should change.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A) A separate "Schedule Settings" page in Administration (as the build plan says).
-B) Inside the Edit Location window (as the design pictures showed).
+          <t>A) Confirmed - more than one range per day, with the overlap warning; the build plan should change.
+B) No - one range per day only in the first release; "Add hours" is for later.
 C) Something else (please explain).</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -595,27 +574,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Can a technician have a split working day (two time ranges)?</t>
+          <t>Does the problem counter include double-bookings?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>The design pictures show an "Add hours" button so a technician's day can have two working ranges (for example 8-12 and 13-17 - a split shift), with a check that the ranges don't overlap. The engineering plan only stores ONE working range per day for each technician - no second range at all.</t>
+          <t>The schedule flags problems like a shift outside a technician's working hours, and a counter at the top shows how many problems there are. The product write-up also counts a technician being booked on two jobs at the same time ("double-booked") as one of these problems. The engineering build plan treats double-booking as a milder heads-up only - shown on the shift itself, but not counted in that counter at the top.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>In the first release, can a technician's working day have two separate time ranges (a split shift), or just one range per day?</t>
+          <t>When a technician is booked on two jobs at the same time, should that show up in the problem counter and list at the top, or only as a milder warning on the shift itself?</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>A) Just one range per day (as the build plan says) - the "Add hours" idea is for later.
-B) Two (or more) ranges per day, with the overlap check (as the pictures show).
+          <t>A) Yes - double-bookings count in the problem counter and list at the top.
+B) No - double-bookings are only a milder warning on the shift, not in the counter.
 C) Something else (please explain).</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -623,27 +602,27 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>May a technician change other technicians' shifts?</t>
+          <t>Do meeting hours also count toward the "OT" tag and the hover breakdown?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Everyone who can see the schedule sees ALL technicians' shifts. For making changes, the engineering plan adds a restriction for certain technician-type users: if their account is set to "own data only", they can create and change ONLY their own shifts - trying to change someone else's is refused. The product write-up does not mention this restriction.</t>
+          <t>You confirmed that meeting hours DO use up a technician's time, so a 2-hour meeting makes the day's busy bar 2 hours fuller. Separately, the schedule shows a small "OT" tag on a day when one single technician goes over their own hours for that day, and a hover note that breaks the day down technician by technician. The product write-up says the day's busy bar includes meeting hours, but it does not say whether meeting hours also feed that "OT" tag and that hover breakdown - it calls the overtime signal "separate and independent".</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Should a technician-type user (with the "own data only" setting) be able to change only their OWN shifts, while seeing everyone's?</t>
+          <t>Should meeting hours also count toward the "OT" tag and the per-technician hover breakdown, or only toward the day's overall busy bar?</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>A) Yes - such users can change only their own shifts (as the build plan says). We will then add a test for it.
-B) No - anyone who can edit the schedule can change anyone's shifts.
+          <t>A) Yes - meeting hours count everywhere: the busy bar, the "OT" tag, and the hover breakdown.
+B) No - only the day's busy bar; the "OT" tag and the hover breakdown count job shifts only.
 C) Something else (please explain).</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -651,27 +630,28 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Do calendar events use up a technician's time? (asked July 27 - still open, and the newest answer reverses your earlier one)</t>
+          <t>Can a meeting be created for a whole department instead of one technician?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>We asked this on July 27 and it is still open - and it now needs your confirmation more than before. Earlier you told us events (like meetings) do NOT use up a technician's available time, but you would check. Since then, a comment answer on the requirements page (dated July 23) says the opposite - event hours DO count. The engineering build plan follows that comment: a 2-hour meeting counts as 2 hours less free time for the day (though it never raises a warning by itself). Because this reverses your earlier answer, we need you to confirm it. Also good to know: many old events already in the system would start counting on day one, so technicians may suddenly look busier - that would be expected, not a fault.</t>
+          <t>Today a meeting is placed on one named technician's row. Shops often hold a meeting (a safety briefing, a training session) for a whole department at once. The product write-up does not mention this at all, so we do not know whether to test it. Engineering's working assumption is that a whole-department meeting would NOT use up each technician's time - but that is an engineering guess, not your decision.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>When a technician has an event (like a 2-hour meeting), should those hours count against how busy that technician looks on the day, or not?</t>
+          <t>Should someone be able to create a meeting for a whole department in the first release - and if yes, does it use up each of those technicians' time?</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>A) Yes - event hours count toward how busy the technician is (the newer comment's answer, and what engineering is building).
-B) No - events do not count (your earlier answer).
-C) Something else (please explain).</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
+          <t>A) Yes - a whole-department meeting, and it uses up each of those technicians' time.
+B) Yes - a whole-department meeting, but it does not use up their time (it is just shown on their rows).
+C) No - one technician at a time only in the first release.
+D) Something else (please explain).</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -679,26 +659,55 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Should the shift pop-up have a 'Reassign' button? (asked July 27 - still open)</t>
+          <t>Can a meeting cover a whole day, and how should it show on the schedule?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>We asked this on July 27 and it is still open. When you open a scheduled shift, a small pop-up shows its details. The written story still says this pop-up should have a 'Reassign' button to move the shift to a different technician. The newest design pictures removed that button, and the engineering plan is building it WITHOUT the button - moving a shift is done only by dragging it onto another technician.</t>
+          <t>The meeting window has an "all day" switch, so a meeting can be set for a whole day with no start or end time. Now that meeting hours use up a technician's time, we do not know what a whole-day meeting should do - and the product write-up does not say. It also does not say where a whole-day meeting sits on the schedule, since it has no times to position it by. Engineering's working assumption is that a whole-day meeting is shown but uses up no time - again an engineering guess, not your decision.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>For the first release, should the shift pop-up include a 'Reassign' button, or is dragging the shift the only way to move it to another technician?</t>
+          <t>Should a whole-day meeting use up that technician's whole working day, or just be shown on their row without using up any time - and where should it appear?</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>A) Keep the 'Reassign' button in the pop-up (plus dragging) - the written story's way.
-B) No button - moving a shift is done only by dragging it (as the newest pictures show and engineering is building).</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr"/>
+          <t>A) It uses up the whole working day, shown as a band across the top of that technician's row.
+B) It is only shown on the row and uses up no time.
+C) Something else (please explain).</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>If a user hides meetings from the view, do those hours stop counting?</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>There is a display switch called "Events" that shows or hides meetings on the schedule. Meeting hours now count toward each day's busy bar. The product write-up does not say what should happen to that counting when someone switches meetings off - so the busy bars could either shrink or stay the same, and we cannot tell which is correct.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>When a user hides meetings from the view, should those hours also come OUT of the day's busy bars, or should the bars keep counting them and only the meetings disappear from the screen?</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>A) The hours come out too - the busy bars recalculate as if there were no meetings.
+B) Only the meetings disappear from the screen - the busy bars keep counting their hours.
+C) Something else (please explain).</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -711,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -723,7 +732,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>QA-ONLY - do not send this sheet to the PO. TestRail C-ids from build/schedule/testrail-id-map.csv (Rule 8); link https://shopview.testrail.io/index.php?/cases/view/&lt;id&gt;</t>
+          <t>QA-ONLY - do not send this sheet to the PO. Revised 2026-07-31 against the current product write-up (Confluence version 23, 2026-07-30). TestRail C-ids from build/schedule/testrail-id-map.csv (Standing Rule 8): https://shopview.testrail.io/index.php?/cases/view/&lt;id&gt;</t>
         </is>
       </c>
     </row>
@@ -750,154 +759,290 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>1</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>SCH-EDGE-05 (C30089)
 SCH-SPREAD-07 (C29983)
 SCH-SPREAD-08 (C29984)
-new SCH-SPREAD-11 + SCH-API-02 previews (no C-id yet)</t>
+SCH-SPREAD-11 (C38863)
+SCH-API-02 (C38873)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Source: tech-plan-2026-07-29/Questions-for-Branko-dev.md NQ-1. Tech plan D7 ('skips closures + non-working days (real skipping)') + Phase 7 SpreadDialog E2E 'created series has no shift on the closure day' vs Jira SV-8691 delta D2 (2026-07-27): 'shop closures NOT skipped in V1'. Last-update-wins is ambiguous (plan dated 2026-07-22, handed 2026-07-29).</t>
+          <t>Was NQ-1 (tech-plan-2026-07-29/Questions-for-Branko-dev.md). REFRAMED to a confirmation 2026-07-31: spec 4.5 (Confluence v22, still standing in v23) = 'Shop closures and public holidays are not skipped in V1..' -&gt; the spec now SIDES WITH our cases. Two counter-artefacts remain: spec 12 Edge cases still says closures 'block the spread step' (spec-internal contradiction X1, flagged in requirements.md), and tech plan D7 + Phase-7 E2E build real skipping.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>A -&gt; rewrite SCH-EDGE-05 (closure = skipped + struck through in preview) + SCH-SPREAD-07 expected #3 + SCH-SPREAD-08 reason list. B -&gt; cases stand. Verify LIVE either way.</t>
+          <t>A (confirm) -&gt; cases stand as written; raise the 12 sentence + the build plan as corrections. B -&gt; rewrite SCH-EDGE-05 (closure = skipped + struck through in preview) + SCH-SPREAD-07 expected #3 + SCH-SPREAD-08 reason list. Verify LIVE either way (Rule 12).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SCH-HRS-02 (C38847)
+SCH-HRS-03 (C38848)
+SCH-HRS-04 (C38849)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Was NQ-3. REFRAMED to a confirmation 2026-07-31: spec 4.2 'Hours settings' block (Confluence v19, verbatim: 'a technician's custom schedule in Edit Staff Member, and the shop's business hours in Edit Location') -&gt; the spec now SIDES WITH our cases. Tech plan Phase 2 builds ScheduleSettings.vue in Administration + closures CRUD instead; the plan itself notes the design's Hours Settings file was an empty shell. Closure-day location is spec-silent - hence the sub-ask.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>A (confirm) -&gt; cases stand; the build plan should change; author a closures-CRUD case once he says where closures live. B -&gt; re-home SCH-HRS-02/03/04 to the Schedule Settings page. (SCH-HRS-01/C38846 was merged into SCH-HRS-02 + deleted in the 2026-07-31 consolidation.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SCH-HRS-05 (C38850)
+SCH-HRS-06 (C38851)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Was NQ-4. REFRAMED to a confirmation 2026-07-31: spec 4.2 verbatim "'Add hours' appends more to support split shifts, each removable" + the overlap-validation paragraph (Confluence v19) -&gt; the spec now SIDES WITH our cases. Tech plan 3 staff_working_hours = one start_minute/end_minute per weekday, unique (staff, workplace, day) - no split ranges.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>A (confirm) -&gt; cases stand; the build plan's data model must change. B -&gt; retire/park SCH-HRS-05/06 (pending authorization, Rule 6). (SCH-HRS-07/C38852 was merged into SCH-HRS-06 + deleted in the 2026-07-31 consolidation.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>SCH-CONF-01 (C30023)
 SCH-CONF-05 (C30027)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Source: NQ-2. Tech plan D4: double-booking = FE soft warning, 'not a hard conflict per the locked definition'; BE detector = outside-window/closure/non-working only. vs SV-8697 §4.11 'Double-booked' conflict type + our pill-count expectations.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Was NQ-2 - UNCHANGED, still a genuine open choice. Spec 4.11 conflict-type table lists 'Double-booked' (unchanged in v23); tech plan D4 = double-booking is an FE soft warning, 'not a hard conflict per the locked definition', BE detector covers outside-window/closure/non-working only. Not settled by v23.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>A -&gt; cases stand. B -&gt; rewrite SCH-CONF-01 expected #3/#4 (icon yes, pill no) and adjust SCH-CONF-05's count basis.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>SCH-HRS-01 (C38846)
-SCH-HRS-02 (C38847)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Source: NQ-3. Tech plan Phase 2 (ScheduleSettings.vue in Administration + closures CRUD + View-Options link) vs design/SV-8699 Edit-Location toggle. Plan itself says the design's Hours Settings file was an empty SHELL.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>A -&gt; re-home SCH-HRS-01/02 to the Schedule Settings page + author a closures-CRUD case. B -&gt; cases stand; closures UI location TBD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>SCH-HRS-05 (C38850)
-SCH-HRS-06 (C38851)
-SCH-HRS-07 (C38852)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Source: NQ-4. Tech plan §3 staff_working_hours = one start_minute/end_minute per weekday, unique (staff, workplace, day) - no split ranges. vs SV-8699 verbatim 'Add hours appends more to support split shifts'.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>A -&gt; retire/park SCH-HRS-05..07 (pending authorization). B -&gt; cases stand and the build plan's model must change.</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>SCH-PERM-09 (C30082) context
-a new negative case would be authored only on answer A</t>
+          <t>SCH-CAP-03 (C30032)
+SCH-CAP-04 (C30033)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Source: NQ-5. Tech plan NFR-003/§4: ManageShiftVoter own-data scoping for isRestrictedToOwnData() users; error 'cross-tech own-data violation -&gt; 403'. Spec §14 is silent on WRITE scoping (SCH-PERM-09 covers VIEW only - no contradiction, but unconfirmed).</t>
+          <t>NEW 2026-07-31 (internal id A1) - opened by Branko's own events-&gt;capacity answer. Spec 4.12 (v19) includes event time in the aggregate total but calls overtime 'a separate per-technician signal, and the two are independent' and never says whether event hours feed the OT test or the per-tech hover breakdown. Spec silent (Rule 15). Could also be answered by dev.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>A -&gt; author the own-data write-negative (UI + API halves). B -&gt; no case; confirm no 403 surprises at VIU.</t>
+          <t>A -&gt; assert event hours in the OT tag + hover breakdown on SCH-CAP-03/04. B -&gt; assert shift-hours-only on both. Until answered, both cases assert only what IS pinned (neither outcome).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>6</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>SCH-CAP-01 (C30030)
+SCH-CAP-02 (C30031)
+SCH-CAP-03 (C30032)
+SCH-CAP-04 (C30033)
+SCH-EVT-08 (C30615)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>NEW 2026-07-31 (internal id A2). Department-level events are not in the spec at all (4.10 Events + 8 Event entity are per-technician: rowKey (tech)). The tech plan's working default is 'department-assigned events do NOT count toward capacity' - an engineering default, not a product ruling.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>A -&gt; author a department-event capacity case + extend SCH-CAP-01..04. B -&gt; author a department-event display-only case. C -&gt; no case; confirm the UI offers no department option at VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>SCH-EVT-08 (C30615)
-SCH-CAP-01..04 (C30030-C30033)
+SCH-EVT-03 (C30018)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NEW 2026-07-31 (internal id A3). Spec 4.10 gives the Event modal an 'all-day toggle' and 8 gives Event an allDay field, but nothing says what an unbounded all-day event does to capacity or where it renders. Spec silent. Tech plan working default = 'visual only'.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>A -&gt; author an all-day-event capacity case (full working day consumed) + a render-position expectation. B -&gt; assert display-only, zero capacity, on SCH-EVT-08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>SCH-VIEW-05 (C30046)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>NEW 2026-07-31 (internal id A7, found in the Rule-28 sweep). Only became a question once events started consuming capacity (v19). Spec 9 View Options 'Events' toggle says only 'Shows non-WO event blocks on the grid' - silent on the capacity consequence. Spec silent.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>A -&gt; SCH-VIEW-05 also asserts the capacity bars recalculate. B -&gt; SCH-VIEW-05 asserts the bars are unchanged. Today it deliberately asserts only 'event blocks disappear from the grid while shifts remain' - neither outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED
+was Q6</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>SCH-EVT-08 (C30615)
+SCH-CAP-01 (C30030)
+SCH-CAP-02 (C30031)
+SCH-CAP-03 (C30032)
+SCH-CAP-04 (C30033)
 SCH-CONF-01 (C30023)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>HELD item D1 (re-ask of PO-Questions-Branko-Schedule-2026-07-27 Q1). RECONCILIATION Delta D1 + tech plan D5: plan BUILDS 'events count toward capacity, but are NOT conflict-checked', citing a PRD Confluence Q&amp;A comment answer of 2026-07-23 that REVERSES Branko's earlier 'No'. Engineering defaults pending product confirm: department-assigned events do NOT count; unbounded all-day events are visual-only. ~9,684 migrated legacy events would raise capacity bars at cutover (expected, not a bug).</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>A -&gt; rewrite SCH-EVT-08 to 'counts toward capacity but not conflict-checked'; flip the events-excluded note on SCH-CAP-01..04; firm up SCH-CONF-01. B -&gt; keep cases as-is (events excluded from capacity). Verify LIVE at VIU either way (Rule 12).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>D1 - 'Do calendar events use up a technician's time?' ANSWERED 2026-07-31, option A. Branko VERBATIM: "A) 4.12 PRD is explicit: 'Event time is included in the utilization total alongside shifts, so meetings and training consume capacity.' A 2-hour meeting consumes 2 hours of capacity. Note the split in 4.11: events count toward capacity but are not conflict-checked. The design and the written plan already agree; this only needs confirming, not deciding." Corroborated word-for-word by Confluence v19 4.12. Source: branko-answers-2026-07-31/answers-ingested.md Q1.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>REMOVED from the reader-facing sheet - DO NOT ASK AGAIN. HOLD LIFTS; reverses his earlier 'No'. Follow-on spec-silent items became reader-facing Q5/Q6/Q7/Q8 above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ANSWERED
+was Q7</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>SCH-MODAL-08 (C30015)
 SCH-REAS-01 (C30052)
-SCH-REAS-02 (retired/deleted 2026-07-22, no C-id)</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>HELD item D4 (re-ask of PO-Questions-Branko-Schedule-2026-07-27 Q2). RECONCILIATION Delta D4: Jira story SV-8695 lists a modal Reassign action; the design prototype removed it (SCH-REAS-02 retired on the design's authority, Branko Q0); tech plan BUILDS drag-only ('no modal reassign action', 'PRD wins over prototype drift') = supports B.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>A (story wins) -&gt; re-add a modal-Reassign case (SCH-MODAL-08 back to Delete+Reassign) and un-retire SCH-REAS-02; the plan must change. B (design/plan wins) -&gt; keep cases as-is and the story text should be corrected. Do not change cases until Branko rules.</t>
+(SCH-REAS-02 retired/deleted 2026-07-22)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>D4 - "Should the shift pop-up have a 'Reassign' button?" ANSWERED 2026-07-31, option B. Branko VERBATIM: "B - No button". Corroborated by Confluence v23 (2026-07-30) deleting 'and Reassign to another technician' from 4.9. Source: branko-answers-2026-07-31/answers-ingested.md Q2.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>REMOVED from the reader-facing sheet - DO NOT ASK AGAIN. HOLD LIFTS; confirms our cases as written. Jira SV-8695 still lists a modal Reassign action -&gt; SV-8695 is now the stale artefact; tell Branko/dev.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RE-ROUTED
+was Q5</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>SCH-PERM-09 (C30082) context; a new negative case would be authored only on answer 'yes'</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>NQ-5 - 'May a technician change other technicians' shifts?' RE-ROUTED TO ENGINEERING/DEV 2026-07-31. Branko on the sibling backend-scope question: "I'm not sure if this question is for me Bilal." - and he is right, this is enforcement/scoping, not a product decision. Spec 14.3 rules out own-only VIEWING and is SILENT on WRITING (re-verified against the live v23 body). Tech plan NFR-003/4 builds ManageShiftVoter own-data scoping ('cross-tech own-data violation -&gt; 403').</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>REMOVED from the reader-facing PO sheet - it is not a product question. Logged as needing a DEV answer in tech-plan-2026-07-29/Questions-for-Branko-dev.md. On 'yes, scoped' -&gt; author the own-data write-negative (UI + backend halves). On 'no' -&gt; no case; confirm no 403 surprises at VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>SCH-EXP-01 (C38853)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Week Export DESCOPED by Branko 2026-07-31, VERBATIM: 'No. There is nothing about this in the PRD, not in the future requirements.' Independently corroborated by a full-text scan of Confluence v23 (no export/print item in 6 Grid toolbar, 9 View options, or 15 Future considerations). NOT a question - a pending retire decision.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>RETIRE CANDIDATE - HELD, AWAITING EXPLICIT USER AUTHORIZATION (Rule 6). Nothing deleted. (SCH-EXP-02/C38854 was already merged away + deleted in the 2026-07-31 consolidation.) Known id-map gap: C38853 is absent from testrail-id-map.csv because its local body is flagged Retired while the TestRail case still exists - quote C38853 from the execution log/manifest until the map is reconciled.</t>
         </is>
       </c>
     </row>

--- a/build/schedule/PO-Questions-Branko-Schedule-TechPlan_2026-07-30.xlsx
+++ b/build/schedule/PO-Questions-Branko-Schedule-TechPlan_2026-07-30.xlsx
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Week Export DESCOPED by Branko 2026-07-31, VERBATIM: 'No. There is nothing about this in the PRD, not in the future requirements.' Independently corroborated by a full-text scan of Confluence v23 (no export/print item in 6 Grid toolbar, 9 View options, or 15 Future considerations). NOT a question - a pending retire decision.</t>
+          <t>Week Export DESCOPED by Branko 2026-07-31, VERBATIM: 'No. There is nothing about this in the PRD, not in the future requirements.' Independently corroborated by a full-text scan of Confluence v23 (no export/print item in 6 Grid toolbar, 9 View options, or 15 Future considerations). NOT a question - a closed retire decision.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>RETIRE CANDIDATE - HELD, AWAITING EXPLICIT USER AUTHORIZATION (Rule 6). Nothing deleted. (SCH-EXP-02/C38854 was already merged away + deleted in the 2026-07-31 consolidation.) Known id-map gap: C38853 is absent from testrail-id-map.csv because its local body is flagged Retired while the TestRail case still exists - quote C38853 from the execution log/manifest until the map is reconciled.</t>
+          <t>RETIRED + DELETED 2026-07-31, user-authorized (executed by a parallel pass, folder week-export-retire-2026-07-31): delete_case/38853 -&gt; HTTP 200, re-GET -&gt; HTTP 400 = verified gone; run 357 165 -&gt; 164 tests, 429 result records intact; section 5406 'Week Export and Printing' now empty but deliberately NOT deleted (cleanup candidate). Active tally 165 -&gt; 164; id-map regenerated to 164, all C-ids re-merged. (SCH-EXP-02/C38854 was already merged away + deleted in the 2026-07-31 consolidation.)</t>
         </is>
       </c>
     </row>
